--- a/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_5AV.xlsx
+++ b/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_5AV.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,10 +58,16 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,24 +97,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -174,11 +174,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,20 +222,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -630,13 +639,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -648,208 +658,132 @@
       <c r="B1" s="14" t="n"/>
       <c r="C1" s="14" t="n"/>
       <c r="D1" s="14" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="E1" s="14" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 5AV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>5AV</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>AMENDAÑO CARFEÑO ARIANA SOFIA</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>5AV</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>AMENDAÑO CARREÑO ARIANA SOFIA</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>5AV</t>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>BACUILIMA SANMARTIN ERIKA ALEJANDRA</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>BACUILIMA SANMARTIN ERIKA ALEJANDRA</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Matemática (Docente: 9.31 vs Sistema: 9.81)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>5AV</t>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>PINTO CRUZ ELIAN ISMAEL</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>GUANUQUIZA CACHIPULLA GUADALUPE DEL ROCIO</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>5AV</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>GUANUQUIZA CARCHIPULLA GUADALUPE DEL ROCIO</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>5AV</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>PINTO CRUZ ELIAN ISMAEL</t>
+          <t>❌ ERROR DE NOTA</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>8.52</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>QUIZHPI CHABLA LUIS MIGUEL</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.76 vs Sistema: 5.79)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>5AV</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>PINTO CRUZ ELIAN ISMAEL</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.95 vs Sistema: 8.52)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>5AV</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>QUIZHPI CHABLA LUIS MIGUEL</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Matemática (Docente: 9.51 vs Sistema: 9.61)</t>
-        </is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>9.609999999999999</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="4">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
